--- a/output/pdf_financials_xlsx/AWI.xlsx
+++ b/output/pdf_financials_xlsx/AWI.xlsx
@@ -10987,7 +10987,11 @@
           <t>Prepaid and deposits (note 7)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -12862,7 +12866,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E91" s="5" t="n">
         <v>0.047364</v>
       </c>

--- a/output/pdf_financials_xlsx/AWI.xlsx
+++ b/output/pdf_financials_xlsx/AWI.xlsx
@@ -900,13 +900,13 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>2.749259</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>3.287743</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>3.239299</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.961902</v>
+        <v>0.212643</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>-0.338778</v>
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.131775</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.45472</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.439282</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -1880,13 +1880,13 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.421499</v>
+        <v>0.289724</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.230298</v>
+        <v>-0.224422</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.473269</v>
+        <v>0.033987</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -1992,13 +1992,13 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.421499</v>
+        <v>0.289724</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.230298</v>
+        <v>-0.224422</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.473269</v>
+        <v>0.033987</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -2048,13 +2048,13 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>7.698028368625939</v>
+        <v>5.291361476709985</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>4.049815804758848</v>
+        <v>-3.94648569477629</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>8.612849181734832</v>
+        <v>0.6185169642203941</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>8.775648</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>9.617723</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>9.205055</v>
@@ -2283,7 +2283,7 @@
         <v>15.775648</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>5.26359</v>
+        <v>14.881313</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>13.23891</v>
@@ -2763,7 +2763,7 @@
         <v>1.277467</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>10.962004</v>
+        <v>1.344281</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>1.470101</v>
@@ -6170,16 +6170,16 @@
         </is>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.186216</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.179506</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.193844</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.234056</v>
       </c>
     </row>
     <row r="125">
@@ -6224,16 +6224,16 @@
         </is>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.186216</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.179506</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.193844</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.234056</v>
       </c>
     </row>
     <row r="126">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -16704,7 +16704,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -19950,7 +19954,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -20094,7 +20098,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
